--- a/docs/dialogues-2026-10-14.xlsx
+++ b/docs/dialogues-2026-10-14.xlsx
@@ -3461,7 +3461,7 @@
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>First time you open the 👑 leader picker  · arena_app.js:8789</t>
+          <t>First time you open the 👑 leader picker  · arena_app.js:8918</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>After a fight, the first time you get a card that can lead (Heroic+); the example uses a Heroic card  · arena_app.js:8800</t>
+          <t>After a fight, the first time you get a card that can lead (Heroic+); the example uses a Heroic card  · arena_app.js:8929</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>The first time the Conquest map opens  · arena_app.js:12044</t>
+          <t>The first time the Conquest map opens  · arena_app.js:12173</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>In a fight, the first time a card needs Lumber  · arena_app.js:26400</t>
+          <t>In a fight, the first time a card needs Lumber  · arena_app.js:26605</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>In a fight, the first time a card needs Lumber  · arena_app.js:26400</t>
+          <t>In a fight, the first time a card needs Lumber  · arena_app.js:26605</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:24136</t>
+          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:24314</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:24136</t>
+          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:24314</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:26424</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:26629</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:26423</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:26628</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:26419</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:26624</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Opening the Codex once card families (phyla) unlock  · arena_app.js:4066</t>
+          <t>Opening the Codex once card families (phyla) unlock  · arena_app.js:4142</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Tapping the old well on Map 0  · arena_app.js:12023</t>
+          <t>Tapping the old well on Map 0  · arena_app.js:12152</t>
         </is>
       </c>
     </row>

--- a/docs/dialogues-2026-10-14.xlsx
+++ b/docs/dialogues-2026-10-14.xlsx
@@ -3461,7 +3461,7 @@
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>First time you open the 👑 leader picker  · arena_app.js:8918</t>
+          <t>First time you open the 👑 leader picker  · arena_app.js:9066</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>After a fight, the first time you get a card that can lead (Heroic+); the example uses a Heroic card  · arena_app.js:8929</t>
+          <t>After a fight, the first time you get a card that can lead (Heroic+); the example uses a Heroic card  · arena_app.js:9077</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>The first time the Conquest map opens  · arena_app.js:12173</t>
+          <t>The first time the Conquest map opens  · arena_app.js:12326</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>In a fight, the first time a card needs Lumber  · arena_app.js:26605</t>
+          <t>In a fight, the first time a card needs Lumber  · arena_app.js:26890</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>In a fight, the first time a card needs Lumber  · arena_app.js:26605</t>
+          <t>In a fight, the first time a card needs Lumber  · arena_app.js:26890</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       <c r="G104" s="2" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:24314</t>
+          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:24568</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
       <c r="G105" s="2" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:24314</t>
+          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:24568</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4177,7 @@
       <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:26629</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:26915</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:26628</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:26914</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:26624</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:26910</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Opening the Codex once card families (phyla) unlock  · arena_app.js:4142</t>
+          <t>Opening the Codex once card families (phyla) unlock  · arena_app.js:4265</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       <c r="G182" s="2" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Tapping the old well on Map 0  · arena_app.js:12152</t>
+          <t>Tapping the old well on Map 0  · arena_app.js:12305</t>
         </is>
       </c>
     </row>

--- a/docs/dialogues-2026-10-14.xlsx
+++ b/docs/dialogues-2026-10-14.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Add your own" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dialogues'!$A$1:$H$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dialogues'!$A$1:$H$195</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3432,7 +3432,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>lesson_leader_rule</t>
+          <t>forge_cobble_dust</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
@@ -3440,67 +3440,71 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>golem</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Cobble, the Forge golem</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>assets/npc/golem.png?v=2a1bc2b6f5</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Only Heroic rarity cards and above can be leader cards.</t>
+          <t>Not enough Dust. Fuse a duplicate or win a few fights, then come back.</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>First time you open the 👑 leader picker  · arena_app.js:9066</t>
+          <t>(not found: maybe unused)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>lesson_leader_rule</t>
+          <t>forge_cobble_gate</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>golem</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Cobble, the Forge golem</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>assets/npc/golem.png?v=2a1bc2b6f5</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>You don't have one yet. Win or pull a Heroic card and I'll let you know.</t>
+          <t>Not yet. That level opens further down the road.</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>(not found: maybe unused)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>lesson_leaders</t>
+          <t>forge_cobble_gold</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
@@ -3508,90 +3512,94 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>golem</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Cobble, the Forge golem</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>assets/npc/golem.png?v=2a1bc2b6f5</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Only Heroic rarity cards and above can be leader cards.</t>
+          <t>Not enough Maple Leaves. The fire eats them too.</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>After a fight, the first time you get a card that can lead (Heroic+); the example uses a Heroic card  · arena_app.js:9077</t>
+          <t>(not found: maybe unused)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>lesson_leaders</t>
+          <t>forge_cobble_intro</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>golem</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Cobble, the Forge golem</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>assets/npc/golem.png?v=2a1bc2b6f5</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Sergeant Bramblefox is Heroic: this one can be your leader!</t>
+          <t>Cobble. I keep the fire. Feed a card Dust and Leaves and I temper it, one level at a time.</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>renderForge()  · arena_app.js:31998</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>lesson_leaders</t>
+          <t>forge_cobble_intro</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>sergeant-bramblefox</t>
+          <t>golem</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Sergeant Bramblefox</t>
+          <t>Cobble, the Forge golem</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>card art: Sergeant Bramblefox</t>
+          <t>assets/npc/golem.png?v=2a1bc2b6f5</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Put me in the 👑 slot and I'll join you once a fight.</t>
+          <t>At level 10 a card hits its limit. Bring duplicates and I can break it, and it climbs again.</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
@@ -3600,75 +3608,79 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>lesson_leaders</t>
+          <t>forge_cobble_limit</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>golem</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Cobble, the Forge golem</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>assets/npc/golem.png?v=2a1bc2b6f5</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>A leader waits beside the board and joins you once a fight. Pick it in the Camp, in the 👑 slot.</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Show me. [tab:deck] | Later.</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr"/>
+          <t>It is not ready to break its limit. Level 10 and enough duplicates first.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>(not found: maybe unused)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>lesson_leaders</t>
+          <t>forge_cobble_mats</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>golem</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Cobble, the Forge golem</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>assets/npc/golem.png?v=2a1bc2b6f5</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Mind you, I am still the best leader you have got.</t>
+          <t>Missing Materia for that one. The Blacksmith can make it.</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>(not found: maybe unused)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>outskirts_reveal</t>
+          <t>forge_cobble_tier</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -3676,158 +3688,162 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>golem</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>Cobble, the Forge golem</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>assets/npc/golem.png?v=2a1bc2b6f5</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>There — the Outskirts. Scouts and stragglers, mostly.</t>
+          <t>My Forge cannot heat that high yet. Upgrade the Forge first.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>The first time the Conquest map opens  · arena_app.js:12326</t>
+          <t>(not found: maybe unused)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>outskirts_reveal</t>
+          <t>lesson_leader_rule</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Mostly. Which means not entirely. We go carefully.</t>
+          <t>Only Heroic rarity cards and above can be leader cards.</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>First time you open the 👑 leader picker  · arena_app.js:9242</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>outskirts_reveal</t>
+          <t>lesson_leader_rule</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>You heard the Marshal. You're with us, aren't you?</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Of course. | What's in it for me?</t>
-        </is>
-      </c>
+          <t>You don't have one yet. Win or pull a Heroic card and I'll let you know.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>outskirts_reveal</t>
+          <t>lesson_leaders</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Good. Then the first patrol is yours.</t>
+          <t>Only Heroic rarity cards and above can be leader cards.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>After a fight, the first time you get a card that can lead (Heroic+); the example uses a Heroic card  · arena_app.js:9286</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>outskirts_reveal</t>
+          <t>lesson_leaders</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Leaves, glory, and the Marshal's eternal respect. Two of those are real.</t>
+          <t>Sergeant Bramblefox is Heroic: this one can be your leader!</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
@@ -3836,30 +3852,30 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>outskirts_reveal</t>
+          <t>lesson_leaders</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>sergeant-bramblefox</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>Sergeant Bramblefox</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Sergeant Bramblefox</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>…Quiet type. I can work with quiet.</t>
+          <t>Put me in the 👑 slot and I'll join you once a fight.</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
@@ -3868,75 +3884,75 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>outskirts_reveal</t>
+          <t>lesson_leaders</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Watch the map. Things turn up when you push further in.</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
+          <t>A leader waits beside the board and joins you once a fight. Pick it in the Camp, in the 👑 slot.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Show me. [tab:deck] | Later.</t>
+        </is>
+      </c>
       <c r="H101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>pitch_lesson_h</t>
+          <t>lesson_leaders</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>aurelia</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Matriarch Aurelia</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>card art: Sunthroat Courier</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Big cards need Lumber. Give up a spare card.</t>
+          <t>Mind you, I am still the best leader you have got.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>In a fight, the first time a card needs Lumber  · arena_app.js:26890</t>
-        </is>
-      </c>
+      <c r="H102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>pitch_lesson_o</t>
+          <t>outskirts_reveal</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
@@ -3959,60 +3975,56 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Big cards need Lumber. Throw a spare card on the pile.</t>
+          <t>There — the Outskirts. Scouts and stragglers, mostly.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>In a fight, the first time a card needs Lumber  · arena_app.js:26890</t>
+          <t>The first time the Conquest map opens  · arena_app.js:12610</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>pitch_spent_h</t>
+          <t>outskirts_reveal</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>aurelia</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Matriarch Aurelia</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>card art: Sunthroat Courier</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>One card a turn. Try again next turn.</t>
+          <t>Mostly. Which means not entirely. We go carefully.</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:24568</t>
-        </is>
-      </c>
+      <c r="H104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>pitch_spent_o</t>
+          <t>outskirts_reveal</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
@@ -4031,115 +4043,107 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>One card a turn. Try again next turn.</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:24568</t>
-        </is>
-      </c>
+          <t>You heard the Marshal. You're with us, aren't you?</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Of course. | What's in it for me?</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>training_wheels_off</t>
+          <t>outskirts_reveal</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>That's everything I can teach you on a quiet road.</t>
+          <t>Good. Then the first patrol is yours.</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>After Tutorial Part 2, the first time</t>
-        </is>
-      </c>
+      <c r="H106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>training_wheels_off</t>
+          <t>outskirts_reveal</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>swiftpaw</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>Captain Swiftpaw</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Otter Scout</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Training is over. No more stopping to explain.</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>I'm ready.</t>
-        </is>
-      </c>
+          <t>Leaves, glory, and the Marshal's eternal respect. Two of those are real.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>training_wheels_off</t>
+          <t>outskirts_reveal</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Read every card you meet. The road will do the rest.</t>
+          <t>…Quiet type. I can work with quiet.</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
@@ -4148,11 +4152,11 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>tut_boomerang</t>
+          <t>outskirts_reveal</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
@@ -4171,20 +4175,16 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Boomerangs come back. They hit twice.</t>
+          <t>Watch the map. Things turn up when you push further in.</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:26915</t>
-        </is>
-      </c>
+      <c r="H109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>tut_fly</t>
+          <t>pitch_lesson_h</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
@@ -4207,20 +4207,20 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>We fly! Ground units miss us half the time.</t>
+          <t>Big cards need Lumber. Give up a spare card.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:26914</t>
+          <t>In a fight, the first time a card needs Lumber  · arena_app.js:27992</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>tut_traveller_cheer</t>
+          <t>pitch_lesson_o</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
@@ -4228,35 +4228,35 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>swiftpaw</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Captain Swiftpaw</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Scout</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>You almost got them! One more push.</t>
+          <t>Big cards need Lumber. Throw a spare card on the pile.</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:26910</t>
+          <t>In a fight, the first time a card needs Lumber  · arena_app.js:27992</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>unlock_arena</t>
+          <t>pitch_spent_h</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
@@ -4264,39 +4264,39 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>vesper</t>
+          <t>aurelia</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Warlord Vesper</t>
+          <t>Matriarch Aurelia</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>card art: Crimson Wing Duelist Cadet</t>
+          <t>card art: Sunthroat Courier</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>An otter with a deck. How quaint. Fight me where it counts.</t>
+          <t>One card a turn. Try again next turn.</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Map feature: The Arena (Map 11 Eyrie Heights)</t>
+          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:25486</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>unlock_arena</t>
+          <t>pitch_spent_o</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
@@ -4315,188 +4315,196 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>The Arena. Strangers, tickets, bad manners.</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>I'm in. [sub:arena] | Later.</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr"/>
+          <t>One card a turn. Try again next turn.</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>In a fight, trying to send a 2nd card to the Graveyard in one turn  · arena_app.js:25486</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>unlock_arena</t>
+          <t>training_wheels_off</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>vesper</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Warlord Vesper</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>card art: Crimson Wing Duelist Cadet</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Of course. Later. They always say later.</t>
+          <t>That's everything I can teach you on a quiet road.</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>After Tutorial Part 2, the first time</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>unlock_arena</t>
+          <t>training_wheels_off</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>vesper</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Warlord Vesper</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>card art: Crimson Wing Duelist Cadet</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Ten tickets a day. Spend them well.</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
+          <t>Training is over. No more stopping to explain.</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>I'm ready.</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>unlock_autobattler</t>
+          <t>training_wheels_off</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Whisper-of-Ash</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>card art: Voidfeather Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>You like games? Here's one. Build an army from nothing. Watch it fight without you.</t>
+          <t>Read every card you meet. The road will do the rest.</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Whisper’s Game (Map 5 Gatorback Swamp)</t>
-        </is>
-      </c>
+      <c r="H116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>unlock_autobattler</t>
+          <t>tut_boomerang</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>swiftpaw</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Whisper-of-Ash</t>
+          <t>Captain Swiftpaw</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>card art: Voidfeather Scout</t>
+          <t>card art: Otter Scout</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Ten wins and you're a legend. Five losses and you're a story.</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Deal.</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr"/>
+          <t>Boomerangs come back. They hit twice.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:28017</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>unlock_autobattler</t>
+          <t>tut_fly</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>aurelia</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Whisper-of-Ash</t>
+          <t>Matriarch Aurelia</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>card art: Voidfeather Scout</t>
+          <t>card art: Sunthroat Courier</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>…Don't tell the Marshal you saw me.</t>
+          <t>We fly! Ground units miss us half the time.</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:28016</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>unlock_backpack</t>
+          <t>tut_traveller_cheer</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
@@ -4519,300 +4527,300 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Psst. You have carried that pack since the Outskirts and never once looked inside.</t>
+          <t>You almost got them! One more push.</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Map feature: A note in your pack (Map 5 Gatorback Swamp)</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:28012</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>unlock_backpack</t>
+          <t>unlock_arena</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>vesper</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Warlord Vesper</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Crimson Wing Duelist Cadet</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Everything you win that isn't a card ends up in there: materia, eggs, packs, coin.</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Show me. [tab:inventory]</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr"/>
+          <t>An otter with a deck. How quaint. Fight me where it counts.</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: The Arena (Map 11 Eyrie Heights)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>unlock_backpack</t>
+          <t>unlock_arena</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>swiftpaw</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Captain Swiftpaw</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Scout</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>It's all in your Inventory now.</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr"/>
+          <t>The Arena. Strangers, tickets, bad manners.</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>I'm in. [sub:arena] | Later.</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>unlock_codex</t>
+          <t>unlock_arena</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>vesper</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Warlord Vesper</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Crimson Wing Duelist Cadet</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>A field book. Every card anyone on this road has ever seen, drawn in by somebody.</t>
+          <t>Of course. Later. They always say later.</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Codex (Map 7 The Morel Hollow)</t>
-        </is>
-      </c>
+      <c r="H122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>unlock_codex</t>
+          <t>unlock_arena</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>vesper</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>Warlord Vesper</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Crimson Wing Duelist Cadet</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Half the pages are blank.</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Then we fill them. [tab:codex]</t>
-        </is>
-      </c>
+          <t>Ten tickets a day. Spend them well.</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>unlock_codex</t>
+          <t>unlock_autobattler</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Whisper-of-Ash</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Voidfeather Scout</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>A page fills itself the first time you meet the card. Keep your eyes open.</t>
+          <t>You like games? Here's one. Build an army from nothing. Watch it fight without you.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Whisper’s Game (Map 5 Gatorback Swamp)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>unlock_deck</t>
+          <t>unlock_autobattler</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>Whisper-of-Ash</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Voidfeather Scout</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>An armoury tent. About time.</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Camp (Map 0 Bramblewood Outskirts)</t>
-        </is>
-      </c>
+          <t>Ten wins and you're a legend. Five losses and you're a story.</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Deal.</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>unlock_deck</t>
+          <t>unlock_autobattler</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>Whisper-of-Ash</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Voidfeather Scout</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Choose who marches with you. Twenty cards, no more, no less.</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Show me.</t>
-        </is>
-      </c>
+          <t>…Don't tell the Marshal you saw me.</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>unlock_deck</t>
+          <t>unlock_backpack</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>And maybe stop bringing the slow ones.</t>
+          <t>Psst. You have carried that pack since the Outskirts and never once looked inside.</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: A note in your pack (Map 5 Gatorback Swamp)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>unlock_fieldkit</t>
+          <t>unlock_backpack</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
@@ -4831,24 +4839,24 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>The road gets mean from here. I packed you a field kit: draughts, kindling, a scout's map, a fire pot and a few odds and ends.</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: The traveller's kit (Map 12 The Briar Maze)</t>
-        </is>
-      </c>
+          <t>Everything you win that isn't a card ends up in there: materia, eggs, packs, coin.</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Show me. [tab:inventory]</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>unlock_fieldkit</t>
+          <t>unlock_backpack</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
@@ -4867,24 +4875,20 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Save it for a fight you can't win any other way. One item a fight, and I'll top you up a little each day.</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>Show me. [tab:inventory]</t>
-        </is>
-      </c>
+          <t>It's all in your Inventory now.</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>unlock_fieldkit</t>
+          <t>unlock_codex</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
@@ -4903,160 +4907,164 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>In a fight, look for the 🎒 beside your Lumber.</t>
+          <t>A field book. Every card anyone on this road has ever seen, drawn in by somebody.</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Codex (Map 7 The Morel Hollow)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>unlock_forge</t>
+          <t>unlock_codex</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>swiftpaw</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Captain Swiftpaw</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Scout</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>The Foundry’s smiths will temper anything you bring them, for a price.</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: The Forge (Map 11 Eyrie Heights)</t>
-        </is>
-      </c>
+          <t>Half the pages are blank.</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Then we fill them. [tab:codex]</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>unlock_forge</t>
+          <t>unlock_codex</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Dust, leaves and spare copies. Bring all three.</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>Show me the anvil. [forge]</t>
-        </is>
-      </c>
+          <t>A page fills itself the first time you meet the card. Keep your eyes open.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>unlock_forge</t>
+          <t>unlock_deck</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Feed a card enough of itself and, one day, it breaks its own limit.</t>
+          <t>An armoury tent. About time.</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Camp (Map 0 Bramblewood Outskirts)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>unlock_gauntlet</t>
+          <t>unlock_deck</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>vesper</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Warlord Vesper</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>card art: Crimson Wing Duelist Cadet</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>You win in the Arena. Fine. Can you keep winning?</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Gauntlet Gate (Map 16 The Pinewood Taiga)</t>
-        </is>
-      </c>
+          <t>Choose who marches with you. Twenty cards, no more, no less.</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Show me.</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>unlock_gauntlet</t>
+          <t>unlock_deck</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
@@ -5075,56 +5083,56 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Ten in a row? That’s the Gauntlet.</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Bring it.</t>
-        </is>
-      </c>
+          <t>And maybe stop bringing the slow ones.</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>unlock_gauntlet</t>
+          <t>unlock_fieldkit</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>vesper</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Warlord Vesper</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>card art: Crimson Wing Duelist Cadet</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Lose once and you start again from nothing. That’s the point.</t>
+          <t>The road gets mean from here. I packed you a field kit: draughts, kindling, a scout's map, a fire pot and a few odds and ends.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: The traveller's kit (Map 12 The Briar Maze)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>unlock_mapcodex</t>
+          <t>unlock_fieldkit</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
@@ -5143,24 +5151,24 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Somebody has been drawing the road as you go. Every map, and what the weather does on each.</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Map Codex (Map 11 Eyrie Heights)</t>
-        </is>
-      </c>
+          <t>Save it for a fight you can't win any other way. One item a fight, and I'll top you up a little each day.</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Show me. [tab:inventory]</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>unlock_mapcodex</t>
+          <t>unlock_fieldkit</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
@@ -5179,7 +5187,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>It is in your Codex now, under Maps.</t>
+          <t>In a fight, look for the 🎒 beside your Lumber.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
@@ -5188,7 +5196,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>unlock_market</t>
+          <t>unlock_forge</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
@@ -5211,20 +5219,20 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Every trader who ever crossed these maps ends up here sooner or later. So do their cards.</t>
+          <t>The Foundry’s smiths will temper anything you bring them, for a price.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Map feature: Flea Market (~map31)</t>
+          <t>Map feature: The Forge (Map 11 Eyrie Heights)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>unlock_market</t>
+          <t>unlock_forge</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
@@ -5232,175 +5240,175 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>The Flea Market. Buy from other players, sell what you don't need. Haggling is frowned upon. Mostly.</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr"/>
+          <t>Dust, leaves and spare copies. Bring all three.</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Show me the anvil. [forge]</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>unlock_nest</t>
+          <t>unlock_forge</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>An old nest. Somebody kept their cards here once.</t>
+          <t>Feed a card enough of itself and, one day, it breaks its own limit.</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Nest (Map 2 Pebble Beach)</t>
-        </is>
-      </c>
+      <c r="H141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>unlock_nest</t>
+          <t>unlock_gauntlet</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>vesper</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>Warlord Vesper</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Crimson Wing Duelist Cadet</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Everything you win ends up in yours now. Want a look?</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>Show me. [tab:nest]</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr"/>
+          <t>You win in the Arena. Fine. Can you keep winning?</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Gauntlet Gate (Map 16 The Pinewood Taiga)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>unlock_nest</t>
+          <t>unlock_gauntlet</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>swiftpaw</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>Captain Swiftpaw</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Otter Scout</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Count it twice. Soldiers lose things.</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr"/>
+          <t>Ten in a row? That’s the Gauntlet.</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Bring it.</t>
+        </is>
+      </c>
       <c r="H143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>unlock_phyla</t>
+          <t>unlock_gauntlet</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>vesper</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Warlord Vesper</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Crimson Wing Duelist Cadet</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Notice how the cards fall into families? Otters, badgers and moles are all Beasts. Bees and scorpions are Arthropods.</t>
+          <t>Lose once and you start again from nothing. That’s the point.</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>Opening the Codex once card families (phyla) unlock  · arena_app.js:4265</t>
-        </is>
-      </c>
+      <c r="H144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>unlock_phyla</t>
+          <t>unlock_mapcodex</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
@@ -5419,111 +5427,111 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Those families are phyla. The Codex can sort and filter by them now.</t>
+          <t>Somebody has been drawing the road as you go. Every map, and what the weather does on each.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Map Codex (Map 11 Eyrie Heights)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>unlock_questboard</t>
+          <t>unlock_mapcodex</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>A proper quest board. Real requests from real folk, not lodge orders.</t>
+          <t>It is in your Codex now, under Maps.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Quest Board (Map 8 Caves &amp; Alcoves)</t>
-        </is>
-      </c>
+      <c r="H146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>unlock_questboard</t>
+          <t>unlock_market</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>So when somebody on the road says “could you…”, it goes up here?</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>Sounds like work. [quests:errands]</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr"/>
+          <t>Every trader who ever crossed these maps ends up here sooner or later. So do their cards.</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Flea Market (~map31)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>unlock_questboard</t>
+          <t>unlock_market</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Errands. Small favours, small rewards. They add up.</t>
+          <t>The Flea Market. Buy from other players, sell what you don't need. Haggling is frowned upon. Mostly.</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr"/>
@@ -5532,7 +5540,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>unlock_quests</t>
+          <t>unlock_nest</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
@@ -5540,35 +5548,35 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>swiftpaw</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>Captain Swiftpaw</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Otter Scout</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>The notice board. Orders from the lodge — every day, every week.</t>
+          <t>An old nest. Somebody kept their cards here once.</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Map feature: Notices (Map 4 Sunken Hollow)</t>
+          <t>Map feature: Nest (Map 2 Pebble Beach)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>unlock_quests</t>
+          <t>unlock_nest</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
@@ -5591,12 +5599,12 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>The first few pay well. The rest… pay.</t>
+          <t>Everything you win ends up in yours now. Want a look?</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>I'll take them. [quests]</t>
+          <t>Show me. [tab:nest]</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
@@ -5604,7 +5612,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>unlock_quests</t>
+          <t>unlock_nest</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
@@ -5627,7 +5635,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Do the work, get the leaves. That's the whole system.</t>
+          <t>Count it twice. Soldiers lose things.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr"/>
@@ -5636,7 +5644,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>unlock_raid</t>
+          <t>unlock_phyla</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
@@ -5644,35 +5652,35 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>aurelia</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Matriarch Aurelia</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>card art: Sunthroat Courier</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Even the Dominion cannot fell that thing alone.</t>
+          <t>Notice how the cards fall into families? Otters, badgers and moles are all Beasts. Bees and scorpions are Arthropods.</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Map feature: Raid Banner (Map 13 The Redwood Deep)</t>
+          <t>Opening the Codex once card families (phyla) unlock  · arena_app.js:4409</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>unlock_raid</t>
+          <t>unlock_phyla</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
@@ -5680,22 +5688,22 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Then we chip at it together. Every deck that fights wears it down.</t>
+          <t>Those families are phyla. The Codex can sort and filter by them now.</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr"/>
@@ -5704,79 +5712,83 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>unlock_raid</t>
+          <t>unlock_questboard</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>aurelia</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Matriarch Aurelia</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>card art: Sunthroat Courier</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Will you stand with your enemies, if only for an afternoon?</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>For an afternoon. | Never.</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr"/>
+          <t>A proper quest board. Real requests from real folk, not lodge orders.</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Quest Board (Map 8 Caves &amp; Alcoves)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>unlock_raid</t>
+          <t>unlock_questboard</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>aurelia</t>
+          <t>swiftpaw</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Matriarch Aurelia</t>
+          <t>Captain Swiftpaw</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>card art: Sunthroat Courier</t>
+          <t>card art: Otter Scout</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Then stand beside them and pretend. It works the same.</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="inlineStr"/>
+          <t>So when somebody on the road says “could you…”, it goes up here?</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Sounds like work. [quests:errands]</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>unlock_raid</t>
+          <t>unlock_questboard</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
@@ -5795,7 +5807,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>One shared foe. One shared prize when it falls.</t>
+          <t>Errands. Small favours, small rewards. They add up.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr"/>
@@ -5804,7 +5816,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop</t>
+          <t>unlock_quests</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
@@ -5812,35 +5824,35 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Ah! A customer. Or a soldier. In this war they're the same thing.</t>
+          <t>The notice board. Orders from the lodge — every day, every week.</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Map feature: Traveller’s Cart (Map 5 Gatorback Swamp)</t>
+          <t>Map feature: Notices (Map 4 Sunken Hollow)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop</t>
+          <t>unlock_quests</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
@@ -5848,27 +5860,27 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>swiftpaw</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Captain Swiftpaw</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Scout</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Packs, trinkets, the odd rumour. Interested?</t>
+          <t>The first few pay well. The rest… pay.</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Let's trade. | Rumours?</t>
+          <t>I'll take them. [quests]</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr"/>
@@ -5876,7 +5888,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop</t>
+          <t>unlock_quests</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
@@ -5884,22 +5896,22 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Only that the Crown didn't fly away on its own. But you didn't hear it from me.</t>
+          <t>Do the work, get the leaves. That's the whole system.</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr"/>
@@ -5908,103 +5920,103 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop</t>
+          <t>unlock_raid</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>aurelia</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Matriarch Aurelia</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Sunthroat Courier</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Leaves on the counter, please.</t>
+          <t>Even the Dominion cannot fell that thing alone.</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Raid Banner (Map 13 The Redwood Deep)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop2</t>
+          <t>unlock_raid</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>peddler</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Old Cinder, the Ember Peddler</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>card art: Quarry Mole</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Mind the cinders. The Foundry's fire is right behind me, and it's still warm. So are the prices.</t>
+          <t>Then we chip at it together. Every deck that fights wears it down.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Ember Peddler (Map 8 Caves &amp; Alcoves)</t>
-        </is>
-      </c>
+      <c r="H161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop2</t>
+          <t>unlock_raid</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>peddler</t>
+          <t>aurelia</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Old Cinder, the Ember Peddler</t>
+          <t>Matriarch Aurelia</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>card art: Quarry Mole</t>
+          <t>card art: Sunthroat Courier</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Tidemire Chests. Five cards, one you've never held. The Cart can't carry them this far up.</t>
+          <t>Will you stand with your enemies, if only for an afternoon?</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>Show me. | Who are you?</t>
+          <t>For an afternoon. | Never.</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr"/>
@@ -6012,30 +6024,30 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop2</t>
+          <t>unlock_raid</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>peddler</t>
+          <t>aurelia</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Old Cinder, the Ember Peddler</t>
+          <t>Matriarch Aurelia</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>card art: Quarry Mole</t>
+          <t>card art: Sunthroat Courier</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>A mole who walked the wrong way out of a mine and kept going. You'll find my stall with the Cart's.</t>
+          <t>Then stand beside them and pretend. It works the same.</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr"/>
@@ -6044,30 +6056,30 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop2</t>
+          <t>unlock_raid</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>shieldback</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>High Marshal Shieldback</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Shieldback</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Competition! Wonderful. We'll share a counter. Shops, plural, now.</t>
+          <t>One shared foe. One shared prize when it falls.</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr"/>
@@ -6076,7 +6088,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop3</t>
+          <t>unlock_shop</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
@@ -6099,20 +6111,20 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>A caravan with gold on the wheels. They only sell the good cases.</t>
+          <t>Ah! A customer. Or a soldier. In this war they're the same thing.</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Map feature: Gilded Caravan (Map 13 The Redwood Deep)</t>
+          <t>Map feature: Traveller’s Cart (Map 5 Gatorback Swamp)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop3</t>
+          <t>unlock_shop</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
@@ -6120,27 +6132,27 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Highcrest Cases. I’ve heard of those.</t>
+          <t>Packs, trinkets, the odd rumour. Interested?</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>Let’s look. [tab:shop]</t>
+          <t>Let's trade. | Rumours?</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
@@ -6148,7 +6160,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>unlock_shop3</t>
+          <t>unlock_shop</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
@@ -6171,7 +6183,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>Look first. Buy second. Regret never.</t>
+          <t>Only that the Crown didn't fly away on its own. But you didn't hear it from me.</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr"/>
@@ -6180,11 +6192,11 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>unlock_skillcodex</t>
+          <t>unlock_shop</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
@@ -6203,132 +6215,124 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>A field guide to tricks. Every skill you have run into, and what beats it.</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>Show me. [codex:skills]</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Skill Codex (Map 9 The Kelp Mangroves)</t>
-        </is>
-      </c>
+          <t>Leaves on the counter, please.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>unlock_skillcodex</t>
+          <t>unlock_shop2</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>peddler</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Old Cinder, the Ember Peddler</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Quarry Mole</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>It is a new page in your Codex: Skills.</t>
+          <t>Mind the cinders. The Foundry's fire is right behind me, and it's still warm. So are the prices.</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Ember Peddler (Map 8 Caves &amp; Alcoves)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>unlock_stomp</t>
+          <t>unlock_shop2</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>peddler</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Old Cinder, the Ember Peddler</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Quarry Mole</t>
         </is>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Hoofprints, pawprints, clawprints. Everything that trains up here trains on this field.</t>
-        </is>
-      </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Stomping Grounds (Map 21 The Quiet Summit)</t>
-        </is>
-      </c>
+          <t>Tidemire Chests. Five cards, one you've never held. The Cart can't carry them this far up.</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Show me. | Who are you?</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>unlock_stomp</t>
+          <t>unlock_shop2</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>peddler</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Old Cinder, the Ember Peddler</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Quarry Mole</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>The Stomping Grounds. Bring your Hero: level it, spend its points, pick its skills.</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>Show me. [tab:stomp]</t>
-        </is>
-      </c>
+          <t>A mole who walked the wrong way out of a mine and kept going. You'll find my stall with the Cart's.</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>unlock_stomp</t>
+          <t>unlock_shop2</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
@@ -6347,7 +6351,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Mind the ruts. Some of them are mine.</t>
+          <t>Competition! Wonderful. We'll share a counter. Shops, plural, now.</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr"/>
@@ -6356,7 +6360,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>unlock_tavern</t>
+          <t>unlock_shop3</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
@@ -6379,20 +6383,20 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>A tavern, this far out. Warm fire, long tables, and a keeper who has heard every road story twice.</t>
+          <t>A caravan with gold on the wheels. They only sell the good cases.</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Map feature: The Tavern (Map 14 Savanna Reaches)</t>
+          <t>Map feature: Gilded Caravan (Map 13 The Redwood Deep)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>unlock_tavern</t>
+          <t>unlock_shop3</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
@@ -6400,27 +6404,27 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>swiftpaw</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Captain Swiftpaw</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Otter Scout</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Rest here when you have earned it: every 20 different fights you clear, the keeper will stretch your stamina a little further.</t>
+          <t>Highcrest Cases. I’ve heard of those.</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Show me. [tavern]</t>
+          <t>Let’s look. [tab:shop]</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr"/>
@@ -6428,7 +6432,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>unlock_tavern</t>
+          <t>unlock_shop3</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
@@ -6451,7 +6455,7 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Max Energy, raised one cup at a time.</t>
+          <t>Look first. Buy second. Regret never.</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr"/>
@@ -6460,7 +6464,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>unlock_testlab</t>
+          <t>unlock_skillcodex</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
@@ -6468,35 +6472,39 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Whisper-of-Ash</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>card art: Voidfeather Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Psst. A tent full of tables. Nobody fights for real in here.</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="inlineStr"/>
+          <t>A field guide to tricks. Every skill you have run into, and what beats it.</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Show me. [codex:skills]</t>
+        </is>
+      </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Map feature: Test Lab (Map 21 The Quiet Summit)</t>
+          <t>Map feature: Skill Codex (Map 9 The Kelp Mangroves)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>unlock_testlab</t>
+          <t>unlock_skillcodex</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -6504,71 +6512,71 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Whisper-of-Ash</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>card art: Voidfeather Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Put any cards down, see what they do. Nothing you win, nothing you lose.</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>Let me try. [sub:sandbox]</t>
-        </is>
-      </c>
+          <t>It is a new page in your Codex: Skills.</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>unlock_testlab</t>
+          <t>unlock_stomp</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Whisper-of-Ash</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>card art: Voidfeather Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>Experiments only. The Marshal calls it “cheating”. I call it homework.</t>
+          <t>Hoofprints, pawprints, clawprints. Everything that trains up here trains on this field.</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Stomping Grounds (Map 21 The Quiet Summit)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>unlock_wanderer</t>
+          <t>unlock_stomp</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
@@ -6587,60 +6595,56 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>Someone made camp here. Someone who doesn’t stay anywhere long.</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>Map feature: Wanderer’s Camp (Map 13 The Redwood Deep)</t>
-        </is>
-      </c>
+          <t>The Stomping Grounds. Bring your Hero: level it, spend its points, pick its skills.</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Show me. [tab:stomp]</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>unlock_wanderer</t>
+          <t>unlock_stomp</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>The wandering trader! The one with the mystery boosters.</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>Where are they?</t>
-        </is>
-      </c>
+          <t>Mind the ruts. Some of them are mine.</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>unlock_wanderer</t>
+          <t>unlock_tavern</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
@@ -6659,75 +6663,79 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Somewhere on the road, on some days. When you find them, they’ll sell you five. No more.</t>
+          <t>A tavern, this far out. Warm fire, long tables, and a keeper who has heard every road story twice.</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: The Tavern (Map 14 Savanna Reaches)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>well_m1</t>
+          <t>unlock_tavern</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Huh. The old well. Otters drew water here long before the border war.</t>
-        </is>
-      </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
-        <is>
-          <t>Tapping the old well on Map 0  · arena_app.js:12305</t>
-        </is>
-      </c>
+          <t>Rest here when you have earned it: every 20 different fights you clear, the keeper will stretch your stamina a little further.</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Show me. [tavern]</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>well_m1</t>
+          <t>unlock_tavern</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>traveller</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>The Wandering Traveller</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Wandering Traveller</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>And hummingbirds drank from the bucket when nobody was looking. Nobody minded, back then.</t>
+          <t>Max Energy, raised one cup at a time.</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr"/>
@@ -6736,98 +6744,102 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>well_m1</t>
+          <t>unlock_testlab</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>traveller</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>The Wandering Traveller</t>
+          <t>Whisper-of-Ash</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>card art: Wandering Traveller</t>
+          <t>card art: Voidfeather Scout</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>Toss a leaf in, they say, and the Bramblewood remembers who was kind to it.</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>Toss in a leaf. | Keep walking.</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr"/>
+          <t>Psst. A tent full of tables. Nobody fights for real in here.</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Test Lab (Map 21 The Quiet Summit)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>well_m1</t>
+          <t>unlock_testlab</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>swiftpaw</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Captain Swiftpaw</t>
+          <t>Whisper-of-Ash</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Scout</t>
+          <t>card art: Voidfeather Scout</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
-          <t>…Did it just splash back?</t>
-        </is>
-      </c>
-      <c r="G185" s="2" t="inlineStr"/>
+          <t>Put any cards down, see what they do. Nothing you win, nothing you lose.</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Let me try. [sub:sandbox]</t>
+        </is>
+      </c>
       <c r="H185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>well_m1</t>
+          <t>unlock_testlab</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>shieldback</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>High Marshal Shieldback</t>
+          <t>Whisper-of-Ash</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>card art: Otter Shieldback</t>
+          <t>card art: Voidfeather Scout</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>Good. Superstition never won a skirmish.</t>
+          <t>Experiments only. The Marshal calls it “cheating”. I call it homework.</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr"/>
@@ -6836,37 +6848,309 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
+          <t>unlock_wanderer</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>traveller</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>The Wandering Traveller</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>card art: Wandering Traveller</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Someone made camp here. Someone who doesn’t stay anywhere long.</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Map feature: Wanderer’s Camp (Map 13 The Redwood Deep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>unlock_wanderer</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>swiftpaw</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Captain Swiftpaw</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>card art: Otter Scout</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>The wandering trader! The one with the mystery boosters.</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Where are they?</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>unlock_wanderer</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>traveller</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>The Wandering Traveller</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>card art: Wandering Traveller</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Somewhere on the road, on some days. When you find them, they’ll sell you five. No more.</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
           <t>well_m1</t>
         </is>
       </c>
-      <c r="B187" s="2" t="n">
+      <c r="B190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>swiftpaw</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Captain Swiftpaw</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>card art: Otter Scout</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Huh. The old well. Otters drew water here long before the border war.</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Tapping the old well on Map 0  · arena_app.js:12589</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>well_m1</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>shieldback</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>High Marshal Shieldback</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>card art: Otter Shieldback</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>And hummingbirds drank from the bucket when nobody was looking. Nobody minded, back then.</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>well_m1</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>traveller</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>The Wandering Traveller</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>card art: Wandering Traveller</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Toss a leaf in, they say, and the Bramblewood remembers who was kind to it.</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Toss in a leaf. | Keep walking.</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>well_m1</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>swiftpaw</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Captain Swiftpaw</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>card art: Otter Scout</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>…Did it just splash back?</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>well_m1</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>shieldback</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>High Marshal Shieldback</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>card art: Otter Shieldback</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Good. Superstition never won a skirmish.</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>well_m1</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C187" s="2" t="inlineStr">
+      <c r="C195" s="2" t="inlineStr">
         <is>
           <t>traveller</t>
         </is>
       </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>The Wandering Traveller</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>card art: Wandering Traveller</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F195" s="2" t="inlineStr">
         <is>
           <t>Wells are patient. So are the friends you make on both sides of the river.</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H187"/>
+  <autoFilter ref="A1:H195"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6877,7 +7161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7154,6 +7438,23 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>assets/npc/hedgehog.png?v=f4811b5832</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>golem</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cobble, the Forge golem</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>assets/npc/golem.png?v=2a1bc2b6f5</t>
         </is>
       </c>
     </row>

--- a/docs/dialogues-2026-10-14.xlsx
+++ b/docs/dialogues-2026-10-14.xlsx
@@ -3569,7 +3569,7 @@
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>renderForge()  · arena_app.js:31998</t>
+          <t>renderForge()  · arena_app.js:32006</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>In a fight, the first time a card needs Lumber  · arena_app.js:27992</t>
+          <t>In a fight, the first time a card needs Lumber  · arena_app.js:28000</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>In a fight, the first time a card needs Lumber  · arena_app.js:27992</t>
+          <t>In a fight, the first time a card needs Lumber  · arena_app.js:28000</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:28017</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:28025</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:28016</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:28024</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Tutorial fights: remarks from your side  · arena_app.js:28012</t>
+          <t>Tutorial fights: remarks from your side  · arena_app.js:28020</t>
         </is>
       </c>
     </row>
